--- a/data/trans_dic/IP12B$herida-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,54</t>
+          <t>0,0; 30,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,1</t>
+          <t>0,0; 40,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 64,09</t>
+          <t>7,78; 68,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,03</t>
+          <t>0,0; 25,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,02</t>
+          <t>0,0; 29,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 46,47</t>
+          <t>4,7; 49,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 19,36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,77</t>
+          <t>0,0; 24,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,38</t>
+          <t>0,0; 28,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,88</t>
+          <t>0,0; 18,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,76</t>
+          <t>0,0; 19,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,03</t>
+          <t>0,0; 15,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 76,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,56</t>
+          <t>0,0; 35,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,6</t>
+          <t>0,0; 52,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,02</t>
+          <t>0,0; 21,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,46</t>
+          <t>0,0; 52,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,09</t>
+          <t>0,0; 28,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 30,32</t>
+          <t>3,04; 30,98</t>
         </is>
       </c>
     </row>
@@ -1117,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,96</t>
+          <t>0,0; 57,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,24 +1148,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,53</t>
+          <t>0,0; 50,8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,46</t>
+          <t>0,0; 46,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,77</t>
+          <t>0,0; 37,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,05</t>
+          <t>0,0; 54,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,75</t>
+          <t>0,0; 23,86</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,2</t>
+          <t>0,0; 17,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,64</t>
+          <t>0,0; 30,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,92</t>
+          <t>0,0; 37,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,35</t>
+          <t>0,0; 20,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,87; 18,41</t>
+          <t>1,85; 17,59</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 9,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,28</t>
+          <t>2,09; 13,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,2</t>
+          <t>1,47; 12,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,3</t>
+          <t>2,36; 13,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,71</t>
+          <t>2,75; 16,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,81</t>
+          <t>1,57; 8,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,49</t>
+          <t>1,81; 8,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,0</t>
+          <t>3,57; 11,51</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2837</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3205</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>640; 5604</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2592</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3956</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>619; 6455</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3738</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2555</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3503</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2566</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3120</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4002</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2307</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2867</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3223</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5136</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2759</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>594; 6049</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2572</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1784</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3198</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2325</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3894</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2660</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2577</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2405</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4219</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3901</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4133</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>440; 4194</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3576</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>7146</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4230</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4015</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1151; 7592</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>685; 5818</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1499; 8841</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1318; 7746</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1426; 7980</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2255; 10719</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>3680; 11856</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$herida-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -688,37 +688,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,94</t>
+          <t>0,0; 31,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,61</t>
+          <t>0,0; 42,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 68,12</t>
+          <t>7,29; 62,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,57</t>
+          <t>0,0; 28,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,05</t>
+          <t>0,0; 31,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 49,0</t>
+          <t>4,49; 43,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,36</t>
+          <t>0,0; 20,47</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,79</t>
+          <t>0,0; 24,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,86</t>
+          <t>0,0; 23,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,46</t>
+          <t>0,0; 23,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,34</t>
+          <t>0,0; 15,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,37</t>
+          <t>0,0; 17,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,74</t>
+          <t>0,0; 37,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,26</t>
+          <t>0,0; 49,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,06</t>
+          <t>0,0; 20,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,19</t>
+          <t>0,0; 48,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,49</t>
+          <t>0,0; 34,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 30,98</t>
+          <t>2,97; 33,2</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,01</t>
+          <t>0,0; 57,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,8</t>
+          <t>0,0; 60,96</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,18</t>
+          <t>0,0; 59,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,96</t>
+          <t>0,0; 37,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,87</t>
+          <t>0,0; 62,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,86</t>
+          <t>0,0; 30,21</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,74</t>
+          <t>0,0; 14,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,37</t>
+          <t>0,0; 33,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,94</t>
+          <t>0,0; 37,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,99</t>
+          <t>0,0; 23,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 17,59</t>
+          <t>1,9; 19,25</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,64</t>
+          <t>0,0; 9,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,77</t>
+          <t>2,18; 13,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,46</t>
+          <t>1,47; 11,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 13,91</t>
+          <t>1,96; 13,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,75; 16,18</t>
+          <t>2,68; 14,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,81</t>
+          <t>1,44; 8,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,59</t>
+          <t>1,75; 7,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,51</t>
+          <t>3,59; 11,61</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1871,37 +1871,37 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2837</t>
+          <t>0; 2862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3205</t>
+          <t>0; 3326</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>640; 5604</t>
+          <t>600; 5135</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2592</t>
+          <t>0; 2885</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3956</t>
+          <t>0; 4328</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>619; 6455</t>
+          <t>591; 5721</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3738</t>
+          <t>0; 3952</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2555</t>
+          <t>0; 2576</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3503</t>
+          <t>0; 2822</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2566</t>
+          <t>0; 3217</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3120</t>
+          <t>0; 2542</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 4524</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2867</t>
+          <t>0; 2986</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3041</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3223</t>
+          <t>0; 3157</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5136</t>
+          <t>0; 4793</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2759</t>
+          <t>0; 3380</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>594; 6049</t>
+          <t>581; 6481</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2572</t>
+          <t>0; 2574</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3198</t>
+          <t>0; 3837</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2325</t>
+          <t>0; 3012</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3894</t>
+          <t>0; 3824</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2660</t>
+          <t>0; 3032</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2577</t>
+          <t>0; 3262</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2405</t>
+          <t>0; 2018</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4219</t>
+          <t>0; 4692</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3901</t>
+          <t>0; 3841</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 4133</t>
+          <t>0; 4586</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>440; 4194</t>
+          <t>452; 4590</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4230</t>
+          <t>0; 4251</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 4015</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1151; 7592</t>
+          <t>1200; 7458</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>685; 5818</t>
+          <t>686; 5499</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1499; 8841</t>
+          <t>1248; 8726</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1318; 7746</t>
+          <t>1284; 7162</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1426; 7980</t>
+          <t>1306; 7770</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2255; 10719</t>
+          <t>2181; 9965</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3680; 11856</t>
+          <t>3701; 11959</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$herida-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>7,25%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,44; 64,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,22</t>
+          <t>0,0; 32,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 62,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,46</t>
+          <t>0,0; 32,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,77</t>
+          <t>0,0; 30,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 43,43</t>
+          <t>5,15; 46,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,47</t>
+          <t>0,0; 20,69</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,94%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,25</t>
+          <t>0,0; 23,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,13</t>
+          <t>0,0; 28,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,76</t>
+          <t>0,0; 17,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,37</t>
+          <t>0,0; 18,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>25,7%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,36</t>
+          <t>0,0; 48,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,63</t>
+          <t>0,0; 22,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -965,22 +965,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>16,9%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,7</t>
+          <t>0,0; 35,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,91</t>
+          <t>0,0; 47,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 33,2</t>
+          <t>2,91; 30,32</t>
         </is>
       </c>
     </row>
@@ -1075,22 +1075,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>37,11%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>13,42%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,05</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 57,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,96</t>
+          <t>0,0; 51,53</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 46,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,29</t>
+          <t>0,0; 30,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 54,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,21</t>
+          <t>0,0; 32,75</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1405,22 +1405,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>3,35%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,88</t>
+          <t>0,0; 36,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,37</t>
+          <t>0,0; 22,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,29</t>
+          <t>0,0; 21,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 19,25</t>
+          <t>1,87; 18,41</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6,15%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>1,44; 12,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>2,18; 14,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,53</t>
+          <t>2,7; 15,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,77</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,96; 13,73</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,96</t>
+          <t>2,05; 13,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,58</t>
+          <t>1,52; 8,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,98</t>
+          <t>1,94; 8,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,61</t>
+          <t>3,68; 12,0</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>802</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>664</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2481</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3244</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>612; 5272</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2862</t>
+          <t>0; 3246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3326</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>600; 5135</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2885</t>
+          <t>0; 2983</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4328</t>
+          <t>0; 4088</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>591; 5721</t>
+          <t>679; 6121</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3952</t>
+          <t>0; 3994</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>697</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2576</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2822</t>
+          <t>0; 3321</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2553</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3217</t>
+          <t>0; 3445</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2542</t>
+          <t>0; 2865</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4524</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2081,27 +2081,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2134,27 +2134,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>777</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>656</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2307</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3022</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2772</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3041</t>
+          <t>0; 2994</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3157</t>
+          <t>0; 3370</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2254,22 +2254,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2307,22 +2307,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>1663</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4793</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3380</t>
+          <t>0; 4671</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>581; 6481</t>
+          <t>567; 5920</t>
         </is>
       </c>
     </row>
@@ -2470,22 +2470,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>605</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2574</t>
+          <t>0; 1784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1784</t>
+          <t>0; 2614</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3837</t>
+          <t>0; 3244</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>787</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2339</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3824</t>
+          <t>0; 3156</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2620</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3262</t>
+          <t>0; 3537</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2959,22 +2959,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>455</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4257</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2018</t>
+          <t>0; 3796</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4692</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3841</t>
+          <t>0; 3011</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 4586</t>
+          <t>0; 4205</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>452; 4590</t>
+          <t>446; 4388</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>3388</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>3875</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>3759</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4251</t>
+          <t>674; 5700</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>1385; 9087</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1200; 7458</t>
+          <t>1293; 7517</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>686; 5499</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1248; 8726</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1284; 7162</t>
+          <t>1129; 7318</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1306; 7770</t>
+          <t>1378; 7981</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2181; 9965</t>
+          <t>2418; 10596</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3701; 11959</t>
+          <t>3787; 12362</t>
         </is>
       </c>
     </row>
